--- a/questions.xlsx
+++ b/questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-english-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4E0D5D-D4CC-45B5-8EC1-977F66655A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45271E5F-A04D-4820-922F-94AF6027A528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="173">
   <si>
     <t>例文</t>
   </si>
@@ -466,39 +466,6 @@
     <t>We need to get a (         ) answer from him.</t>
   </si>
   <si>
-    <t>私の夏休みは</t>
-  </si>
-  <si>
-    <t>これらの古本は今日は</t>
-  </si>
-  <si>
-    <t>京都にいたとき</t>
-  </si>
-  <si>
-    <t>家の中に入るときは</t>
-  </si>
-  <si>
-    <t>今日</t>
-  </si>
-  <si>
-    <t>私は彼と何度も</t>
-  </si>
-  <si>
-    <t>多くの人々が</t>
-  </si>
-  <si>
-    <t>その店は午前</t>
-  </si>
-  <si>
-    <t>彼は</t>
-  </si>
-  <si>
-    <t>昨夜</t>
-  </si>
-  <si>
-    <t>日本では学校は</t>
-  </si>
-  <si>
     <t>He   (         )   his arm while he was playing basketball.</t>
   </si>
   <si>
@@ -651,7 +618,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,6 +663,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -705,7 +680,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -756,11 +731,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -778,6 +768,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1092,452 +1085,452 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>138</v>
-      </c>
-      <c r="C5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>149</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C6" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C14" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B18" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
-      <c r="C22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C22" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s">
         <v>45</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
-      </c>
-      <c r="C27" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s">
         <v>52</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B32" t="s">
-        <v>143</v>
-      </c>
-      <c r="C32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C32" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
         <v>60</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
         <v>63</v>
       </c>
-      <c r="C36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C36" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
         <v>65</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
         <v>67</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
         <v>69</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
         <v>71</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B41" t="s">
         <v>73</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="9" t="s">
         <v>74</v>
       </c>
     </row>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-english-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45271E5F-A04D-4820-922F-94AF6027A528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C8D9F6-7057-46F0-AFF4-E22523EE5006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="英単語リスト" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="245">
   <si>
     <t>例文</t>
   </si>
@@ -263,191 +263,191 @@
   </si>
   <si>
     <t>We need to get a (         ) answer from him.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>My summer vacation is from  (         )  10th.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>These old books are 30  (         )  cheaper today.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>While I was in Kyoto, I visited many  (         ) .</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Take off your  (         )  when you enter the house.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>We had the same trouble in the  (         )  .</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Is the   (         )   in this room good for you?</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>My aunt gave me some useful   (         )  .</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>I was   (         )   in front of so many people.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>He has great   (         )   in Japanese painting.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>English is the world's   (         )   language.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>There was a   (         )   on the first day of school.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>We had a   (         )   school lunch today.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>What   (         )   do you like the best?</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>I   (         )   e-mails with him many times.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Do you put   (         )   in your coffee?</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Ken looks like an   (         )   when he wears a suit.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Please write your name with a black   (         )  .</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Can you show me your   (         )  ?</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>I   (         )   why Ann didn't come to the party.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Many people   (         )   by e-mail.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>She injured her right   (         )   in the tennis match.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>The soup in the pot   (         )   good.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>I'd like to see   (         )   Matsumoto.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>I went to an   (         )   festival.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">The store opens at 10:30   (         )  </t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>My father is   (         )   my plan to study abroad.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>We must   (         )   the cost of our product.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>The   (         )   was crowded with soccer fans.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>He   (         )   a new planet a hundred years ago.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Last night, I   (         )   the last bus and took a taxi.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Do you have this shirt in a smaller   (         )  ?</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>The medicine had a bad   (         )   on me.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>The   (         )   are eating grass on the farm.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>School starts in   (         )   in Japan.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Let's   (         )   the date for the next practice game.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>My favorite band is playing on the   (         )  .</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>The   (         )   at the hotel was excellent.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>The moon is a   (         )   of the earth.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>He   (         )   his arm while he was playing basketball.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>temples</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>exchanged</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>smells</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">a.m. </t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>discovered</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>missed</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>cows</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>空欄に入る答え</t>
@@ -460,170 +460,408 @@
     <rPh sb="5" eb="6">
       <t>コタ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>We need to get a (         ) answer from him.</t>
-  </si>
-  <si>
-    <t>He   (         )   his arm while he was playing basketball.</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>sentence</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>word</t>
   </si>
   <si>
-    <t>temples</t>
-  </si>
-  <si>
-    <t>exchanged</t>
-  </si>
-  <si>
-    <t>smells</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a.m. </t>
-  </si>
-  <si>
-    <t>discovered</t>
-  </si>
-  <si>
-    <t>missed</t>
-  </si>
-  <si>
-    <t>cows</t>
-  </si>
-  <si>
     <t>meaning</t>
   </si>
   <si>
-    <t>My summer vacation is from  (         )  10th.</t>
-  </si>
-  <si>
-    <t>These old books are 30  (         )  cheaper today.</t>
-  </si>
-  <si>
-    <t>While I was in Kyoto, I visited many  (         ) .</t>
-  </si>
-  <si>
-    <t>Take off your  (         )  when you enter the house.</t>
-  </si>
-  <si>
-    <t>We had the same trouble in the  (         )  .</t>
-  </si>
-  <si>
-    <t>Is the   (         )   in this room good for you?</t>
-  </si>
-  <si>
-    <t>My aunt gave me some useful   (         )  .</t>
-  </si>
-  <si>
-    <t>I was   (         )   in front of so many people.</t>
-  </si>
-  <si>
-    <t>He has great   (         )   in Japanese painting.</t>
-  </si>
-  <si>
-    <t>English is the world's   (         )   language.</t>
-  </si>
-  <si>
-    <t>There was a   (         )   on the first day of school.</t>
-  </si>
-  <si>
-    <t>We had a   (         )   school lunch today.</t>
-  </si>
-  <si>
-    <t>What   (         )   do you like the best?</t>
-  </si>
-  <si>
-    <t>I   (         )   e-mails with him many times.</t>
-  </si>
-  <si>
-    <t>Do you put   (         )   in your coffee?</t>
-  </si>
-  <si>
-    <t>Ken looks like an   (         )   when he wears a suit.</t>
-  </si>
-  <si>
-    <t>Please write your name with a black   (         )  .</t>
-  </si>
-  <si>
-    <t>Can you show me your   (         )  ?</t>
-  </si>
-  <si>
-    <t>I   (         )   why Ann didn't come to the party.</t>
-  </si>
-  <si>
-    <t>Many people   (         )   by e-mail.</t>
-  </si>
-  <si>
-    <t>She injured her right   (         )   in the tennis match.</t>
-  </si>
-  <si>
-    <t>The soup in the pot   (         )   good.</t>
-  </si>
-  <si>
-    <t>I'd like to see   (         )   Matsumoto.</t>
-  </si>
-  <si>
-    <t>I went to an   (         )   festival.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The store opens at 10:30   (         )  </t>
-  </si>
-  <si>
-    <t>My father is   (         )   my plan to study abroad.</t>
-  </si>
-  <si>
-    <t>We must   (         )   the cost of our product.</t>
-  </si>
-  <si>
-    <t>The   (         )   was crowded with soccer fans.</t>
-  </si>
-  <si>
-    <t>He   (         )   a new planet a hundred years ago.</t>
-  </si>
-  <si>
-    <t>Last night, I   (         )   the last bus and took a taxi.</t>
-  </si>
-  <si>
-    <t>Do you have this shirt in a smaller   (         )  ?</t>
-  </si>
-  <si>
-    <t>The medicine had a bad   (         )   on me.</t>
-  </si>
-  <si>
-    <t>The   (         )   are eating grass on the farm.</t>
-  </si>
-  <si>
-    <t>School starts in   (         )   in Japan.</t>
-  </si>
-  <si>
-    <t>Let's   (         )   the date for the next practice game.</t>
-  </si>
-  <si>
-    <t>My favorite band is playing on the   (         )  .</t>
-  </si>
-  <si>
-    <t>The   (         )   at the hotel was excellent.</t>
-  </si>
-  <si>
-    <t>The moon is a   (         )   of the earth.</t>
+    <t>This room has a nice (      ) of the sea.</t>
+  </si>
+  <si>
+    <t>Don't(      ) the paintings in this room.</t>
+  </si>
+  <si>
+    <t>I have to write a (        )  on the trip.</t>
+  </si>
+  <si>
+    <t>Please write your name and (        ) here.</t>
+  </si>
+  <si>
+    <t>We should protect (        ).</t>
+  </si>
+  <si>
+    <t>This table is made of (         ).</t>
+  </si>
+  <si>
+    <t>Don't walk on the (         ) .</t>
+  </si>
+  <si>
+    <t>He is standing in the (      ) of the room.</t>
+  </si>
+  <si>
+    <t>There is a coin at the (        ) of the pool.</t>
+  </si>
+  <si>
+    <t>I only read (         ) of the book.</t>
+  </si>
+  <si>
+    <t>I want to go to a (        ) country.</t>
+  </si>
+  <si>
+    <t>You are very (        ).</t>
+  </si>
+  <si>
+    <t>I'm (         ) I'm late.</t>
+  </si>
+  <si>
+    <t>What is the (         ) reason?</t>
+  </si>
+  <si>
+    <t>My cat has been (        ) for two years.</t>
+  </si>
+  <si>
+    <t>He is (        ) in his left eye.</t>
+  </si>
+  <si>
+    <t>The rules of the game are very (      ).</t>
+  </si>
+  <si>
+    <t>The sun is very  (      )  today.</t>
+  </si>
+  <si>
+    <t>It's getting   (      )   outside.</t>
+  </si>
+  <si>
+    <t>It was a very   (      )   afternoon.</t>
+  </si>
+  <si>
+    <t>It is a Japanese   (      )  .</t>
+  </si>
+  <si>
+    <t>I asked a shop   (      )   for help.</t>
+  </si>
+  <si>
+    <t>He is the   (      )   of this house.</t>
+  </si>
+  <si>
+    <t>We have a   (      )   today.</t>
+  </si>
+  <si>
+    <t>My   (      )   is very kind.</t>
+  </si>
+  <si>
+    <t>The doctor is busy with a   (      )  .</t>
+  </si>
+  <si>
+    <t>He wants to be a   (      )  .</t>
+  </si>
+  <si>
+    <t>My father is a computer   (      )  .</t>
+  </si>
+  <si>
+    <t>He is a   (      )   to many people.</t>
+  </si>
+  <si>
+    <t>He is a police   (      )  .</t>
+  </si>
+  <si>
+    <t>Let me give you some   (      )  .</t>
+  </si>
+  <si>
+    <t>The bridge is in   (      )   of falling.</t>
+  </si>
+  <si>
+    <t>We had a big   (      )   last night.</t>
+  </si>
+  <si>
+    <t>The heavy rain caused a   (      )  .</t>
+  </si>
+  <si>
+    <t>She had a car   (      )  .</t>
+  </si>
+  <si>
+    <t>There is an   (      )   in this sentence.</t>
+  </si>
+  <si>
+    <t>I'm in   (      )  .</t>
+  </si>
+  <si>
+    <t>We must stop air   (      )  .</t>
+  </si>
+  <si>
+    <t>We should think about the   (      )  .</t>
+  </si>
+  <si>
+    <t>view</t>
+  </si>
+  <si>
+    <t>touch</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>nature</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>grass</t>
+  </si>
+  <si>
+    <t>middle</t>
+  </si>
+  <si>
+    <t>bottom</t>
+  </si>
+  <si>
+    <t>part</t>
+  </si>
+  <si>
+    <t>foreign</t>
+  </si>
+  <si>
+    <t>lucky</t>
+  </si>
+  <si>
+    <t>sorry</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>dead</t>
+  </si>
+  <si>
+    <t>blind</t>
+  </si>
+  <si>
+    <t>simple</t>
+  </si>
+  <si>
+    <t>bright</t>
+  </si>
+  <si>
+    <t>dark</t>
+  </si>
+  <si>
+    <t>peaceful</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>clerk</t>
+  </si>
+  <si>
+    <t>master</t>
+  </si>
+  <si>
+    <t>guest</t>
+  </si>
+  <si>
+    <t>neighbor</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>scientist</t>
+  </si>
+  <si>
+    <t>engineer</t>
+  </si>
+  <si>
+    <t>hero</t>
+  </si>
+  <si>
+    <t>officer</t>
+  </si>
+  <si>
+    <t>danger</t>
+  </si>
+  <si>
+    <t>earthquake</t>
+  </si>
+  <si>
+    <t>flood</t>
+  </si>
+  <si>
+    <t>accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">error </t>
+  </si>
+  <si>
+    <t>trouble</t>
+  </si>
+  <si>
+    <t>pollution</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>この部屋は海の眺めがいい。</t>
+  </si>
+  <si>
+    <t>この部屋の絵に触らないでください。</t>
+  </si>
+  <si>
+    <t>私は旅行についての報告書を書かなければならない。</t>
+  </si>
+  <si>
+    <t>ここにあなたの名前と住所を書いてください。</t>
+  </si>
+  <si>
+    <t>私たちは自然を守るべきだ。</t>
+  </si>
+  <si>
+    <t>このテーブルは木でできている。</t>
+  </si>
+  <si>
+    <t>芝生の上を歩かないでください。</t>
+  </si>
+  <si>
+    <t>彼は部屋の真ん中に立っている。</t>
+  </si>
+  <si>
+    <t>プールの底にコインがある。</t>
+  </si>
+  <si>
+    <t>私はその本の部分的にしか読んでいない。</t>
+  </si>
+  <si>
+    <t>私は外国へ行きたい。</t>
+  </si>
+  <si>
+    <t>あなたはとても運がいい。</t>
+  </si>
+  <si>
+    <t>遅れてすみません。</t>
+  </si>
+  <si>
+    <t>主な理由は何ですか。</t>
+  </si>
+  <si>
+    <t>私の猫が死んで2年になる。</t>
+  </si>
+  <si>
+    <t>彼は左目が見えない。</t>
+  </si>
+  <si>
+    <t>そのゲームのルールはとても簡単だ。</t>
+  </si>
+  <si>
+    <t>今日は太陽がとてもまぶしい。</t>
+  </si>
+  <si>
+    <t>外は暗くなってきている。</t>
+  </si>
+  <si>
+    <t>とても穏やかな午後だった。</t>
+  </si>
+  <si>
+    <t>それは日本の習慣です。</t>
+  </si>
+  <si>
+    <t>私は店員に助けを求めた。</t>
+  </si>
+  <si>
+    <t>彼はこの家の主人だ。</t>
+  </si>
+  <si>
+    <t>今日はお客さんが来ています。</t>
+  </si>
+  <si>
+    <t>私の隣人はとても親切だ。</t>
+  </si>
+  <si>
+    <t>医者は患者の対応で忙しい。</t>
+  </si>
+  <si>
+    <t>彼は科学者になりたいと思っている。</t>
+  </si>
+  <si>
+    <t>私の父はコンピューター技師だ。</t>
+  </si>
+  <si>
+    <t>彼は多くの人にとっての英雄だ。</t>
+  </si>
+  <si>
+    <t>彼は警察官です。</t>
+  </si>
+  <si>
+    <t>あなたに少し助言をさせてください。</t>
+  </si>
+  <si>
+    <t>その橋は崩れる危険がある。</t>
+  </si>
+  <si>
+    <t>昨夜、大きな地震があった。</t>
+  </si>
+  <si>
+    <t>大雨が洪水を引き起こした。</t>
+  </si>
+  <si>
+    <t>彼女は自動車事故に遭った。</t>
+  </si>
+  <si>
+    <t>この文には誤りがある。</t>
+  </si>
+  <si>
+    <t>私は困っている。</t>
+  </si>
+  <si>
+    <t>私たちは大気汚染を止めなければならない。</t>
+  </si>
+  <si>
+    <t>私たちは環境について考えるべきだ。</t>
+  </si>
+  <si>
+    <t>太陽エネルギーは太陽の光によって作られている。</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  (      )   energy is created by the light of the sun.</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -664,12 +902,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -680,7 +930,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -732,50 +982,77 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{4E47C8BA-3BA1-4897-8849-8180F0358785}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1083,459 +1360,459 @@
     <col min="3" max="3" width="92.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" t="s">
         <v>125</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+      <c r="B10" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+      <c r="B11" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
+      <c r="B12" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
+      <c r="B13" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
+      <c r="B14" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
+      <c r="B15" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
+      <c r="B16" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B17" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>150</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>152</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A23" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A25" t="s">
+      <c r="C32" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A26" t="s">
+      <c r="B33" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A27" t="s">
+      <c r="B34" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B27" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A28" t="s">
+      <c r="B35" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A29" t="s">
+      <c r="B36" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A30" t="s">
+      <c r="B37" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A31" t="s">
+      <c r="B38" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B31" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A32" t="s">
+      <c r="B39" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B32" t="s">
-        <v>132</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A33" t="s">
-        <v>165</v>
-      </c>
-      <c r="B33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A34" t="s">
-        <v>166</v>
-      </c>
-      <c r="B34" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A35" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A36" t="s">
-        <v>168</v>
-      </c>
-      <c r="B36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A37" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A38" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A39" t="s">
-        <v>171</v>
-      </c>
-      <c r="B39" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A40" t="s">
-        <v>172</v>
-      </c>
-      <c r="B40" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A41" t="s">
-        <v>124</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>74</v>
+      <c r="B40" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2010,7 +2287,7 @@
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.27559055118110237" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="81" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-english-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C8D9F6-7057-46F0-AFF4-E22523EE5006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A030B1F2-0D78-4E64-8C88-779178EC9DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="英単語リスト" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
   <si>
     <t>例文</t>
   </si>
@@ -473,374 +473,367 @@
     <t>meaning</t>
   </si>
   <si>
-    <t>This room has a nice (      ) of the sea.</t>
-  </si>
-  <si>
-    <t>Don't(      ) the paintings in this room.</t>
-  </si>
-  <si>
-    <t>I have to write a (        )  on the trip.</t>
-  </si>
-  <si>
-    <t>Please write your name and (        ) here.</t>
-  </si>
-  <si>
-    <t>We should protect (        ).</t>
-  </si>
-  <si>
-    <t>This table is made of (         ).</t>
-  </si>
-  <si>
-    <t>Don't walk on the (         ) .</t>
-  </si>
-  <si>
-    <t>He is standing in the (      ) of the room.</t>
-  </si>
-  <si>
-    <t>There is a coin at the (        ) of the pool.</t>
-  </si>
-  <si>
-    <t>I only read (         ) of the book.</t>
-  </si>
-  <si>
-    <t>I want to go to a (        ) country.</t>
-  </si>
-  <si>
-    <t>You are very (        ).</t>
-  </si>
-  <si>
-    <t>I'm (         ) I'm late.</t>
-  </si>
-  <si>
-    <t>What is the (         ) reason?</t>
-  </si>
-  <si>
-    <t>My cat has been (        ) for two years.</t>
-  </si>
-  <si>
-    <t>He is (        ) in his left eye.</t>
-  </si>
-  <si>
-    <t>The rules of the game are very (      ).</t>
-  </si>
-  <si>
-    <t>The sun is very  (      )  today.</t>
-  </si>
-  <si>
-    <t>It's getting   (      )   outside.</t>
-  </si>
-  <si>
-    <t>It was a very   (      )   afternoon.</t>
-  </si>
-  <si>
-    <t>It is a Japanese   (      )  .</t>
-  </si>
-  <si>
-    <t>I asked a shop   (      )   for help.</t>
-  </si>
-  <si>
-    <t>He is the   (      )   of this house.</t>
-  </si>
-  <si>
-    <t>We have a   (      )   today.</t>
-  </si>
-  <si>
-    <t>My   (      )   is very kind.</t>
-  </si>
-  <si>
-    <t>The doctor is busy with a   (      )  .</t>
-  </si>
-  <si>
-    <t>He wants to be a   (      )  .</t>
-  </si>
-  <si>
-    <t>My father is a computer   (      )  .</t>
-  </si>
-  <si>
-    <t>He is a   (      )   to many people.</t>
-  </si>
-  <si>
-    <t>He is a police   (      )  .</t>
-  </si>
-  <si>
-    <t>Let me give you some   (      )  .</t>
-  </si>
-  <si>
-    <t>The bridge is in   (      )   of falling.</t>
-  </si>
-  <si>
-    <t>We had a big   (      )   last night.</t>
-  </si>
-  <si>
-    <t>The heavy rain caused a   (      )  .</t>
-  </si>
-  <si>
-    <t>She had a car   (      )  .</t>
-  </si>
-  <si>
-    <t>There is an   (      )   in this sentence.</t>
-  </si>
-  <si>
-    <t>I'm in   (      )  .</t>
-  </si>
-  <si>
-    <t>We must stop air   (      )  .</t>
-  </si>
-  <si>
-    <t>We should think about the   (      )  .</t>
-  </si>
-  <si>
     <t>view</t>
   </si>
   <si>
     <t>touch</t>
   </si>
   <si>
-    <t>report</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>nature</t>
-  </si>
-  <si>
-    <t>wood</t>
-  </si>
-  <si>
-    <t>grass</t>
-  </si>
-  <si>
-    <t>middle</t>
-  </si>
-  <si>
-    <t>bottom</t>
-  </si>
-  <si>
-    <t>part</t>
-  </si>
-  <si>
-    <t>foreign</t>
-  </si>
-  <si>
     <t>lucky</t>
   </si>
   <si>
-    <t>sorry</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>dead</t>
-  </si>
-  <si>
-    <t>blind</t>
-  </si>
-  <si>
-    <t>simple</t>
-  </si>
-  <si>
-    <t>bright</t>
-  </si>
-  <si>
-    <t>dark</t>
-  </si>
-  <si>
-    <t>peaceful</t>
-  </si>
-  <si>
-    <t>custom</t>
-  </si>
-  <si>
-    <t>clerk</t>
-  </si>
-  <si>
-    <t>master</t>
-  </si>
-  <si>
-    <t>guest</t>
-  </si>
-  <si>
-    <t>neighbor</t>
-  </si>
-  <si>
-    <t>patient</t>
-  </si>
-  <si>
-    <t>scientist</t>
-  </si>
-  <si>
-    <t>engineer</t>
-  </si>
-  <si>
-    <t>hero</t>
-  </si>
-  <si>
-    <t>officer</t>
-  </si>
-  <si>
-    <t>danger</t>
-  </si>
-  <si>
-    <t>earthquake</t>
-  </si>
-  <si>
-    <t>flood</t>
-  </si>
-  <si>
-    <t>accident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">error </t>
-  </si>
-  <si>
-    <t>trouble</t>
-  </si>
-  <si>
-    <t>pollution</t>
-  </si>
-  <si>
-    <t>environment</t>
-  </si>
-  <si>
     <t>Solar</t>
   </si>
   <si>
-    <t>この部屋は海の眺めがいい。</t>
-  </si>
-  <si>
-    <t>この部屋の絵に触らないでください。</t>
-  </si>
-  <si>
-    <t>私は旅行についての報告書を書かなければならない。</t>
-  </si>
-  <si>
-    <t>ここにあなたの名前と住所を書いてください。</t>
-  </si>
-  <si>
-    <t>私たちは自然を守るべきだ。</t>
-  </si>
-  <si>
-    <t>このテーブルは木でできている。</t>
-  </si>
-  <si>
-    <t>芝生の上を歩かないでください。</t>
-  </si>
-  <si>
-    <t>彼は部屋の真ん中に立っている。</t>
-  </si>
-  <si>
-    <t>プールの底にコインがある。</t>
-  </si>
-  <si>
-    <t>私はその本の部分的にしか読んでいない。</t>
-  </si>
-  <si>
-    <t>私は外国へ行きたい。</t>
-  </si>
-  <si>
-    <t>あなたはとても運がいい。</t>
-  </si>
-  <si>
-    <t>遅れてすみません。</t>
-  </si>
-  <si>
-    <t>主な理由は何ですか。</t>
-  </si>
-  <si>
-    <t>私の猫が死んで2年になる。</t>
-  </si>
-  <si>
-    <t>彼は左目が見えない。</t>
-  </si>
-  <si>
-    <t>そのゲームのルールはとても簡単だ。</t>
-  </si>
-  <si>
-    <t>今日は太陽がとてもまぶしい。</t>
-  </si>
-  <si>
-    <t>外は暗くなってきている。</t>
-  </si>
-  <si>
-    <t>とても穏やかな午後だった。</t>
-  </si>
-  <si>
-    <t>それは日本の習慣です。</t>
-  </si>
-  <si>
-    <t>私は店員に助けを求めた。</t>
-  </si>
-  <si>
-    <t>彼はこの家の主人だ。</t>
-  </si>
-  <si>
-    <t>今日はお客さんが来ています。</t>
-  </si>
-  <si>
-    <t>私の隣人はとても親切だ。</t>
-  </si>
-  <si>
-    <t>医者は患者の対応で忙しい。</t>
-  </si>
-  <si>
-    <t>彼は科学者になりたいと思っている。</t>
-  </si>
-  <si>
-    <t>私の父はコンピューター技師だ。</t>
-  </si>
-  <si>
-    <t>彼は多くの人にとっての英雄だ。</t>
-  </si>
-  <si>
-    <t>彼は警察官です。</t>
-  </si>
-  <si>
-    <t>あなたに少し助言をさせてください。</t>
-  </si>
-  <si>
-    <t>その橋は崩れる危険がある。</t>
-  </si>
-  <si>
-    <t>昨夜、大きな地震があった。</t>
-  </si>
-  <si>
-    <t>大雨が洪水を引き起こした。</t>
-  </si>
-  <si>
-    <t>彼女は自動車事故に遭った。</t>
-  </si>
-  <si>
-    <t>この文には誤りがある。</t>
-  </si>
-  <si>
-    <t>私は困っている。</t>
-  </si>
-  <si>
-    <t>私たちは大気汚染を止めなければならない。</t>
-  </si>
-  <si>
-    <t>私たちは環境について考えるべきだ。</t>
-  </si>
-  <si>
-    <t>太陽エネルギーは太陽の光によって作られている。</t>
-    <rPh sb="0" eb="2">
-      <t>タイヨウ</t>
+    <t>This room has a nice   (        )   of the sea.</t>
+  </si>
+  <si>
+    <t>Don't   (        )   the paintings in this room.</t>
+  </si>
+  <si>
+    <t>I   (        )   her to my parents.</t>
+  </si>
+  <si>
+    <t>The bell   (        )   at noon on weekdays.</t>
+  </si>
+  <si>
+    <t>The   (        )   caught the man outside the bank.</t>
+  </si>
+  <si>
+    <t>He was a young   (        )   leader.</t>
+  </si>
+  <si>
+    <t>I put some   (        )   in the soup.</t>
+  </si>
+  <si>
+    <t>I   (        )   Jun to my house.</t>
+  </si>
+  <si>
+    <t>The shop sells juice in   (        )   cups.</t>
+  </si>
+  <si>
+    <t>We were   (        )   to get tickets for the movie.</t>
+  </si>
+  <si>
+    <t>Those clothes on the rope are   (        )   now.</t>
+  </si>
+  <si>
+    <t>Kay looked at the clock, and   (        )   out of bed.</t>
+  </si>
+  <si>
+    <t>Dr. Yamanaka discovered iPS   (        )  .</t>
+  </si>
+  <si>
+    <t>Miki graduated from high school this   (        )  .</t>
+  </si>
+  <si>
+    <t>My father showed me how to   (        )  .</t>
+  </si>
+  <si>
+    <t>You should read the   (        )   once more.</t>
+  </si>
+  <si>
+    <t>The title of the report is   (        )   on the first page.</t>
+  </si>
+  <si>
+    <t>The water of the   (        )   is very cold in winter.</t>
+  </si>
+  <si>
+    <t>The ticket for the concert is fifty   (        )  .</t>
+  </si>
+  <si>
+    <t>The number of cars is   (        )   in this city.</t>
+  </si>
+  <si>
+    <t>I'm trying to get some   (        )   every day.</t>
+  </si>
+  <si>
+    <t>Ken is the   (        )   of our soccer team.</t>
+  </si>
+  <si>
+    <t>We enjoyed playing   (        )   on the beach.</t>
+  </si>
+  <si>
+    <t>How often do you eat   (        )  ?</t>
+  </si>
+  <si>
+    <t>What is the   (        )   of this jacket?</t>
+  </si>
+  <si>
+    <t>We walked a long   (        )   in the mountains.</t>
+  </si>
+  <si>
+    <t>Many cars and trucks go over the   (        )  .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (        )   has many strong soccer teams.</t>
+  </si>
+  <si>
+    <t>He   (        )   the horses to the field.</t>
+  </si>
+  <si>
+    <t>The next train will come in a   (        )  .</t>
+  </si>
+  <si>
+    <t>Dry your   (        )   after you take a shower.</t>
+  </si>
+  <si>
+    <t>The girl gave a   (        )   to the monkey.</t>
+  </si>
+  <si>
+    <t>Is the river very   (        )  ?</t>
+  </si>
+  <si>
+    <t>The   (        )   is loved by the people in the country.</t>
+  </si>
+  <si>
+    <t>My grandfather told us about the   (        )  .</t>
+  </si>
+  <si>
+    <t>Thank you for the delicious   (        )   this evening.</t>
+  </si>
+  <si>
+    <t>Mrs. Endo is older than her   (        )  .</t>
+  </si>
+  <si>
+    <t>We have a lot of rain in   (        )  .</t>
+  </si>
+  <si>
+    <t>I  don't  like  the  (        )  of  this  fruit  .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (        )  energy is created by the light of the sun.</t>
+  </si>
+  <si>
+    <t>introduced</t>
+  </si>
+  <si>
+    <t>rings</t>
+  </si>
+  <si>
+    <t>police</t>
+  </si>
+  <si>
+    <t xml:space="preserve">national </t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>invited</t>
+  </si>
+  <si>
+    <t>plastic</t>
+  </si>
+  <si>
+    <t>dry</t>
+  </si>
+  <si>
+    <t>jumped</t>
+  </si>
+  <si>
+    <t>cells</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>ski</t>
+  </si>
+  <si>
+    <t>sentence</t>
+  </si>
+  <si>
+    <t>printed</t>
+  </si>
+  <si>
+    <t>ocean</t>
+  </si>
+  <si>
+    <t>dollars</t>
+  </si>
+  <si>
+    <t>increasing</t>
+  </si>
+  <si>
+    <t>exercise</t>
+  </si>
+  <si>
+    <t>captain</t>
+  </si>
+  <si>
+    <t>volleyball</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>led</t>
+  </si>
+  <si>
+    <t>moment</t>
+  </si>
+  <si>
+    <t>hair</t>
+  </si>
+  <si>
+    <t>banana</t>
+  </si>
+  <si>
+    <t>deep</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>war</t>
+  </si>
+  <si>
+    <t>meal</t>
+  </si>
+  <si>
+    <t>husband</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>taste</t>
+  </si>
+  <si>
+    <t>この部屋は海の眺めがよい</t>
+  </si>
+  <si>
+    <t>この部屋の絵に触らないでください</t>
+  </si>
+  <si>
+    <t>私は両親に彼女を紹介した</t>
+  </si>
+  <si>
+    <t>その鐘は平日の正午に鳴る</t>
+  </si>
+  <si>
+    <t>警察はその男を銀行の外でつかまえた</t>
+  </si>
+  <si>
+    <t>彼は若い国の指導者だった</t>
+  </si>
+  <si>
+    <t>私はスープに塩を入れた</t>
+  </si>
+  <si>
+    <t>私は家にジュンを招いた</t>
+  </si>
+  <si>
+    <t>その店はジュースをプラスチック製のコップに入れて売っている</t>
+  </si>
+  <si>
+    <t>その映画のチケットが取れて私たちは運がよかった</t>
+  </si>
+  <si>
+    <t>ロープにかかったそれらの衣類はもう乾いている</t>
+  </si>
+  <si>
+    <t>ケイは時計を見て、ベッドから飛び起きた</t>
+  </si>
+  <si>
+    <t>山中博士はiPS細胞を発見した</t>
+  </si>
+  <si>
+    <t>ミキは今年の3月に高校を卒業した</t>
+  </si>
+  <si>
+    <t>父は私にスキーのしかたを教えてくれた</t>
+  </si>
+  <si>
+    <t>あなたはその文をもう一度読むべきだ</t>
+  </si>
+  <si>
+    <t>その報告書の題名は最初のページに印刷されている</t>
+  </si>
+  <si>
+    <t>海は冬の海の水はとても冷たい</t>
+  </si>
+  <si>
+    <t>コンサートのチケットは50ドルだ</t>
+  </si>
+  <si>
+    <t>この市では車の数が増えている</t>
+  </si>
+  <si>
+    <t>私は毎日、運動をするようにしている</t>
+  </si>
+  <si>
+    <t>ケンは私たちのサッカーチームの主将だ</t>
+  </si>
+  <si>
+    <t>私たちは浜辺でバレーボールを楽しんだ</t>
+  </si>
+  <si>
+    <t>あなたはどのくらいの頻度で肉を食べますか</t>
+  </si>
+  <si>
+    <t>このジャケットの価格はいくらですか</t>
+  </si>
+  <si>
+    <t>私たちは山の中で長い距離を歩いた</t>
+  </si>
+  <si>
+    <t>多くの車とトラックがその橋を渡る</t>
+  </si>
+  <si>
+    <t>イングランドには強いサッカーチームが多い</t>
+  </si>
+  <si>
+    <t>彼はウマを野原へ導いた</t>
+  </si>
+  <si>
+    <t>次の列車がすぐに来ます</t>
+  </si>
+  <si>
+    <t>シャワーを浴びたら、髪を乾かしなさい</t>
+  </si>
+  <si>
+    <t>少女はそのサルにバナナを与えた</t>
+  </si>
+  <si>
+    <t>その川はとても深いですか</t>
+  </si>
+  <si>
+    <t>王はその国のの人々に愛されている</t>
+  </si>
+  <si>
+    <t>祖父は私たちにその戦争について話した</t>
+  </si>
+  <si>
+    <t>今夜はおいしいお食事をありがとう</t>
+  </si>
+  <si>
+    <t>エンドウさんは彼女の夫より年上だ</t>
+  </si>
+  <si>
+    <t>6月は雨が多い</t>
+  </si>
+  <si>
+    <t>太陽エネルギーは太陽の光によってつくられる</t>
+  </si>
+  <si>
+    <t>meat</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>私はこの果物の味が好きではない</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
     </rPh>
-    <rPh sb="8" eb="10">
-      <t>タイヨウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  (      )   energy is created by the light of the sun.</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -908,17 +901,17 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -1014,7 +1007,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1044,6 +1037,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1373,442 +1369,442 @@
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>165</v>
-      </c>
       <c r="C2" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>166</v>
-      </c>
       <c r="C3" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>195</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>196</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>197</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>198</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>199</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>200</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>201</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>242</v>
+      <c r="C40" s="14" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-english-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A030B1F2-0D78-4E64-8C88-779178EC9DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72ACC072-6C86-4E14-93AD-5CFD417F7342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="英単語リスト" sheetId="1" r:id="rId1"/>
@@ -473,368 +473,364 @@
     <t>meaning</t>
   </si>
   <si>
-    <t>view</t>
-  </si>
-  <si>
-    <t>touch</t>
-  </si>
-  <si>
-    <t>lucky</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>This room has a nice   (        )   of the sea.</t>
-  </si>
-  <si>
-    <t>Don't   (        )   the paintings in this room.</t>
-  </si>
-  <si>
-    <t>I   (        )   her to my parents.</t>
-  </si>
-  <si>
-    <t>The bell   (        )   at noon on weekdays.</t>
-  </si>
-  <si>
-    <t>The   (        )   caught the man outside the bank.</t>
-  </si>
-  <si>
-    <t>He was a young   (        )   leader.</t>
-  </si>
-  <si>
-    <t>I put some   (        )   in the soup.</t>
-  </si>
-  <si>
-    <t>I   (        )   Jun to my house.</t>
-  </si>
-  <si>
-    <t>The shop sells juice in   (        )   cups.</t>
-  </si>
-  <si>
-    <t>We were   (        )   to get tickets for the movie.</t>
-  </si>
-  <si>
-    <t>Those clothes on the rope are   (        )   now.</t>
-  </si>
-  <si>
-    <t>Kay looked at the clock, and   (        )   out of bed.</t>
-  </si>
-  <si>
-    <t>Dr. Yamanaka discovered iPS   (        )  .</t>
-  </si>
-  <si>
-    <t>Miki graduated from high school this   (        )  .</t>
-  </si>
-  <si>
-    <t>My father showed me how to   (        )  .</t>
-  </si>
-  <si>
-    <t>You should read the   (        )   once more.</t>
-  </si>
-  <si>
-    <t>The title of the report is   (        )   on the first page.</t>
-  </si>
-  <si>
-    <t>The water of the   (        )   is very cold in winter.</t>
-  </si>
-  <si>
-    <t>The ticket for the concert is fifty   (        )  .</t>
-  </si>
-  <si>
-    <t>The number of cars is   (        )   in this city.</t>
-  </si>
-  <si>
-    <t>I'm trying to get some   (        )   every day.</t>
-  </si>
-  <si>
-    <t>Ken is the   (        )   of our soccer team.</t>
-  </si>
-  <si>
-    <t>We enjoyed playing   (        )   on the beach.</t>
-  </si>
-  <si>
-    <t>How often do you eat   (        )  ?</t>
-  </si>
-  <si>
-    <t>What is the   (        )   of this jacket?</t>
-  </si>
-  <si>
-    <t>We walked a long   (        )   in the mountains.</t>
-  </si>
-  <si>
-    <t>Many cars and trucks go over the   (        )  .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  (        )   has many strong soccer teams.</t>
-  </si>
-  <si>
-    <t>He   (        )   the horses to the field.</t>
-  </si>
-  <si>
-    <t>The next train will come in a   (        )  .</t>
-  </si>
-  <si>
-    <t>Dry your   (        )   after you take a shower.</t>
-  </si>
-  <si>
-    <t>The girl gave a   (        )   to the monkey.</t>
-  </si>
-  <si>
-    <t>Is the river very   (        )  ?</t>
-  </si>
-  <si>
-    <t>The   (        )   is loved by the people in the country.</t>
-  </si>
-  <si>
-    <t>My grandfather told us about the   (        )  .</t>
-  </si>
-  <si>
-    <t>Thank you for the delicious   (        )   this evening.</t>
-  </si>
-  <si>
-    <t>Mrs. Endo is older than her   (        )  .</t>
-  </si>
-  <si>
-    <t>We have a lot of rain in   (        )  .</t>
-  </si>
-  <si>
-    <t>I  don't  like  the  (        )  of  this  fruit  .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  (        )  energy is created by the light of the sun.</t>
-  </si>
-  <si>
-    <t>introduced</t>
-  </si>
-  <si>
-    <t>rings</t>
-  </si>
-  <si>
-    <t>police</t>
-  </si>
-  <si>
-    <t xml:space="preserve">national </t>
-  </si>
-  <si>
-    <t>salt</t>
-  </si>
-  <si>
-    <t>invited</t>
-  </si>
-  <si>
-    <t>plastic</t>
-  </si>
-  <si>
-    <t>dry</t>
-  </si>
-  <si>
-    <t>jumped</t>
-  </si>
-  <si>
-    <t>cells</t>
-  </si>
-  <si>
-    <t>March</t>
-  </si>
-  <si>
-    <t>ski</t>
-  </si>
-  <si>
-    <t>sentence</t>
-  </si>
-  <si>
-    <t>printed</t>
-  </si>
-  <si>
-    <t>ocean</t>
-  </si>
-  <si>
-    <t>dollars</t>
-  </si>
-  <si>
-    <t>increasing</t>
-  </si>
-  <si>
-    <t>exercise</t>
-  </si>
-  <si>
-    <t>captain</t>
-  </si>
-  <si>
-    <t>volleyball</t>
-  </si>
-  <si>
-    <t>bridge</t>
-  </si>
-  <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>led</t>
-  </si>
-  <si>
-    <t>moment</t>
-  </si>
-  <si>
-    <t>hair</t>
-  </si>
-  <si>
-    <t>banana</t>
-  </si>
-  <si>
-    <t>deep</t>
-  </si>
-  <si>
-    <t>king</t>
-  </si>
-  <si>
-    <t>war</t>
-  </si>
-  <si>
-    <t>meal</t>
-  </si>
-  <si>
-    <t>husband</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>taste</t>
-  </si>
-  <si>
-    <t>この部屋は海の眺めがよい</t>
-  </si>
-  <si>
-    <t>この部屋の絵に触らないでください</t>
-  </si>
-  <si>
-    <t>私は両親に彼女を紹介した</t>
-  </si>
-  <si>
-    <t>その鐘は平日の正午に鳴る</t>
-  </si>
-  <si>
-    <t>警察はその男を銀行の外でつかまえた</t>
-  </si>
-  <si>
-    <t>彼は若い国の指導者だった</t>
-  </si>
-  <si>
-    <t>私はスープに塩を入れた</t>
-  </si>
-  <si>
-    <t>私は家にジュンを招いた</t>
-  </si>
-  <si>
-    <t>その店はジュースをプラスチック製のコップに入れて売っている</t>
-  </si>
-  <si>
-    <t>その映画のチケットが取れて私たちは運がよかった</t>
-  </si>
-  <si>
-    <t>ロープにかかったそれらの衣類はもう乾いている</t>
-  </si>
-  <si>
-    <t>ケイは時計を見て、ベッドから飛び起きた</t>
-  </si>
-  <si>
-    <t>山中博士はiPS細胞を発見した</t>
-  </si>
-  <si>
-    <t>ミキは今年の3月に高校を卒業した</t>
-  </si>
-  <si>
-    <t>父は私にスキーのしかたを教えてくれた</t>
-  </si>
-  <si>
-    <t>あなたはその文をもう一度読むべきだ</t>
-  </si>
-  <si>
-    <t>その報告書の題名は最初のページに印刷されている</t>
-  </si>
-  <si>
-    <t>海は冬の海の水はとても冷たい</t>
-  </si>
-  <si>
-    <t>コンサートのチケットは50ドルだ</t>
-  </si>
-  <si>
-    <t>この市では車の数が増えている</t>
-  </si>
-  <si>
-    <t>私は毎日、運動をするようにしている</t>
-  </si>
-  <si>
-    <t>ケンは私たちのサッカーチームの主将だ</t>
-  </si>
-  <si>
-    <t>私たちは浜辺でバレーボールを楽しんだ</t>
-  </si>
-  <si>
-    <t>あなたはどのくらいの頻度で肉を食べますか</t>
-  </si>
-  <si>
-    <t>このジャケットの価格はいくらですか</t>
-  </si>
-  <si>
-    <t>私たちは山の中で長い距離を歩いた</t>
-  </si>
-  <si>
-    <t>多くの車とトラックがその橋を渡る</t>
-  </si>
-  <si>
-    <t>イングランドには強いサッカーチームが多い</t>
-  </si>
-  <si>
-    <t>彼はウマを野原へ導いた</t>
-  </si>
-  <si>
-    <t>次の列車がすぐに来ます</t>
-  </si>
-  <si>
-    <t>シャワーを浴びたら、髪を乾かしなさい</t>
-  </si>
-  <si>
-    <t>少女はそのサルにバナナを与えた</t>
-  </si>
-  <si>
-    <t>その川はとても深いですか</t>
-  </si>
-  <si>
-    <t>王はその国のの人々に愛されている</t>
-  </si>
-  <si>
-    <t>祖父は私たちにその戦争について話した</t>
-  </si>
-  <si>
-    <t>今夜はおいしいお食事をありがとう</t>
-  </si>
-  <si>
-    <t>エンドウさんは彼女の夫より年上だ</t>
-  </si>
-  <si>
-    <t>6月は雨が多い</t>
-  </si>
-  <si>
-    <t>太陽エネルギーは太陽の光によってつくられる</t>
-  </si>
-  <si>
-    <t>meat</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>distance</t>
-  </si>
-  <si>
-    <t>私はこの果物の味が好きではない</t>
-    <rPh sb="0" eb="1">
-      <t>ワタシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <t>（　　） your hands before you eat.</t>
+  </si>
+  <si>
+    <t>I will send you a （　　） of my family.</t>
+  </si>
+  <si>
+    <t>My father leaves the office at five on （　　）.</t>
+  </si>
+  <si>
+    <t>They (      　) after they had lunch in the park.</t>
+  </si>
+  <si>
+    <t>Lisa （　　） us around the school.</t>
+  </si>
+  <si>
+    <t>Our club goes （　　） every summer.</t>
+  </si>
+  <si>
+    <t>Don't get too close to the （　　）!</t>
+  </si>
+  <si>
+    <t>Keiko is （　　） about studying.</t>
+  </si>
+  <si>
+    <t>（　　） has a large population.</t>
+  </si>
+  <si>
+    <t>This event is open to everyone in the （　　）.</t>
+  </si>
+  <si>
+    <t>The school gate will close in （　　） minutes.</t>
+  </si>
+  <si>
+    <t>My aunt stayed with me for a short （　　）.</t>
+  </si>
+  <si>
+    <t>There are many （　　） on the mountain road.</t>
+  </si>
+  <si>
+    <t>（　　　） has many wonderful places to visit.</t>
+  </si>
+  <si>
+    <t>My （　　） type is A.</t>
+  </si>
+  <si>
+    <t>We will have a （　　） party next week.</t>
+  </si>
+  <si>
+    <t>The station is one （　　） away from here.</t>
+  </si>
+  <si>
+    <t>Smoking is not （　　） in this restaurant.</t>
+  </si>
+  <si>
+    <t>Mike will come to Japan at the （　　） of May.</t>
+  </si>
+  <si>
+    <t>These vegetables are very （　　）.</t>
+  </si>
+  <si>
+    <t>Takashi finished running the （　　）.</t>
+  </si>
+  <si>
+    <t>I have a piano lesson every （　　）.</t>
+  </si>
+  <si>
+    <t>This tower is a （　　） of our city.</t>
+  </si>
+  <si>
+    <t>An （　　） fell from the tree to the ground.</t>
+  </si>
+  <si>
+    <t>Our company has become （　　） recently.</t>
+  </si>
+  <si>
+    <t>I often go to the lake for （　　）.　</t>
+  </si>
+  <si>
+    <t>We have a Halloween party every （　　）.　　</t>
+  </si>
+  <si>
+    <t>We must stop when the traffic lights are （　　）.</t>
+  </si>
+  <si>
+    <t>The （　　） studies wild plants on the island　.</t>
+  </si>
+  <si>
+    <t>Her （　　） job is taking care of young children.</t>
+  </si>
+  <si>
+    <t>Have you ever used a （　　） telephone?</t>
+  </si>
+  <si>
+    <t>I read an interesting （　　） in the magazine.</t>
+  </si>
+  <si>
+    <t>Please （　　） the rope hard.</t>
+  </si>
+  <si>
+    <t>What （　　） is that building going to be?</t>
+  </si>
+  <si>
+    <t>Go （　　） down this street.</t>
+  </si>
+  <si>
+    <t>Those bananas came to Japan by （　　）.</t>
+  </si>
+  <si>
+    <t>（　　） cents is half of a dollar.</t>
+  </si>
+  <si>
+    <t>We go back to school in （　　）.</t>
+  </si>
+  <si>
+    <t>The typhoon caused great （　　） to the town.</t>
+  </si>
+  <si>
+    <t>The earth is the third （　　） from the sun.</t>
+  </si>
+  <si>
+    <t>Wash</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>Wednesdays</t>
+  </si>
+  <si>
+    <t>relaxed</t>
+  </si>
+  <si>
+    <t>guided</t>
+  </si>
+  <si>
+    <t>camping</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>serious</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>fifteen</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>rocks</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>blood</t>
+  </si>
+  <si>
+    <t>Christmas</t>
+  </si>
+  <si>
+    <t>kilometer</t>
+  </si>
+  <si>
+    <t>allowed</t>
+  </si>
+  <si>
+    <t>beginning</t>
+  </si>
+  <si>
+    <t>fresh</t>
+  </si>
+  <si>
+    <t>marathon</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>symbol</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>global</t>
+  </si>
+  <si>
+    <t>fishing</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>researcher</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>pull</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>straight</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>Fifty</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>planet</t>
+  </si>
+  <si>
+    <t>食べる前に手を洗いなさい</t>
+  </si>
+  <si>
+    <t>私はあなたに私の家族の写真を1枚送ります</t>
+  </si>
+  <si>
+    <t>父は水曜日には5時に退社する</t>
+  </si>
+  <si>
+    <t>公園で昼食を食べたあと、彼らはくつろいだ</t>
+  </si>
+  <si>
+    <t>リサは学校じゅう私たちを案内してくれた</t>
+  </si>
+  <si>
+    <t>私たちのクラブは毎年夏にキャンプに行く</t>
+  </si>
+  <si>
+    <t>火に近づきすぎないで！</t>
+  </si>
+  <si>
+    <t>ケイコは学習に対してまじめである</t>
+  </si>
+  <si>
+    <t>インドは人口が多い</t>
+  </si>
+  <si>
+    <t>この行事は地域社会のすべての人に開放されている</t>
+  </si>
+  <si>
+    <t>校門はあと15分で閉まる</t>
+  </si>
+  <si>
+    <t>おばは短期間、私の家に滞在した</t>
+  </si>
+  <si>
+    <t>多くの岩が山道にある</t>
+  </si>
+  <si>
+    <t>フランスには多くの訪れるべき素晴らしい場所がある</t>
+  </si>
+  <si>
+    <t>私の血液型はA型だ</t>
+  </si>
+  <si>
+    <t>私たちは来週クリスマスパーティーを開く</t>
+  </si>
+  <si>
+    <t>駅はここから1キロメートル先だ</t>
+  </si>
+  <si>
+    <t>このレストランでは喫煙は許されていない</t>
+  </si>
+  <si>
+    <t>マイクは5月の初めに日本に来るだろう</t>
+  </si>
+  <si>
+    <t>これらの野菜はとても新鮮だ</t>
+  </si>
+  <si>
+    <t>タカシはマラソンを走り終えた</t>
+  </si>
+  <si>
+    <t>私は毎週火曜日にピアノのレッスンがある</t>
+  </si>
+  <si>
+    <t>この塔は私たちの市の象徴だ</t>
+  </si>
+  <si>
+    <t>リンゴが木から地面に落ちた</t>
+  </si>
+  <si>
+    <t>最近、私たちの会社は国際的になった</t>
+  </si>
+  <si>
+    <t>私はよく釣りをしに湖に行く</t>
+  </si>
+  <si>
+    <t>私たちは毎年10月にハロウィーンパーティーを開く</t>
+  </si>
+  <si>
+    <t>信号が黄色のときは、止まらなければならない</t>
+  </si>
+  <si>
+    <t>その研究者はその島の野生植物を研究している</t>
+  </si>
+  <si>
+    <t>彼女の主な仕事は幼い子どもたちの世話をすることだ</t>
+  </si>
+  <si>
+    <t>あなたは公衆電話を使ったことがありますか</t>
+  </si>
+  <si>
+    <t>私はその雑誌でおもしろい記事を読んだ</t>
+  </si>
+  <si>
+    <t>そのロープを強く引いてください</t>
+  </si>
+  <si>
+    <t>あの建物はどんな形になるのですか</t>
+  </si>
+  <si>
+    <t>この通りをまっすぐに行きなさい</t>
+  </si>
+  <si>
+    <t>それらのバナナは船で日本に来た</t>
+  </si>
+  <si>
+    <t>50セントは1ドルの半分だ</t>
+  </si>
+  <si>
+    <t>私たちは9月に学校に戻る</t>
+  </si>
+  <si>
+    <t>台風は町に大きな損害を及ぼした</t>
+  </si>
+  <si>
+    <t>地球は太陽から3番目の惑星だ</t>
   </si>
 </sst>
 </file>
@@ -1369,442 +1365,442 @@
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>244</v>
+        <v>191</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>129</v>
+        <v>205</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-english-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72ACC072-6C86-4E14-93AD-5CFD417F7342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DFBEA1-29AE-4B10-ACA6-E30D147E2590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="332">
   <si>
     <t>例文</t>
   </si>
@@ -463,381 +463,639 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>word</t>
+  </si>
+  <si>
+    <t>meaning</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>serious</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>fifteen</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>blood</t>
+  </si>
+  <si>
+    <t>Christmas</t>
+  </si>
+  <si>
+    <t>kilometer</t>
+  </si>
+  <si>
+    <t>beginning</t>
+  </si>
+  <si>
+    <t>fresh</t>
+  </si>
+  <si>
+    <t>marathon</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>symbol</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>global</t>
+  </si>
+  <si>
+    <t>fishing</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>researcher</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>pull</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>straight</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>planet</t>
+  </si>
+  <si>
+    <t>はっきりした</t>
+  </si>
+  <si>
+    <t>8月</t>
+  </si>
+  <si>
+    <t>パーセント</t>
+  </si>
+  <si>
+    <t>寺院</t>
+  </si>
+  <si>
+    <t>（ふちのない）帽子</t>
+  </si>
+  <si>
+    <t>過去</t>
+  </si>
+  <si>
+    <t>温度、気温</t>
+  </si>
+  <si>
+    <t>忠告、アドバイス</t>
+  </si>
+  <si>
+    <t>神経質な、緊張して</t>
+  </si>
+  <si>
+    <t>技能、技術</t>
+  </si>
+  <si>
+    <t>共通の、ふつうの</t>
+  </si>
+  <si>
+    <t>式典</t>
+  </si>
+  <si>
+    <t>おいしい</t>
+  </si>
+  <si>
+    <t>科目、主題</t>
+  </si>
+  <si>
+    <t>〜を交換する</t>
+  </si>
+  <si>
+    <t>砂糖</t>
+  </si>
+  <si>
+    <t>大人</t>
+  </si>
+  <si>
+    <t>ペン</t>
+  </si>
+  <si>
+    <t>ノート、メモ帳</t>
+  </si>
+  <si>
+    <t>〜かしらと思う</t>
+  </si>
+  <si>
+    <t>コミュニケーションをとる</t>
+  </si>
+  <si>
+    <t>足</t>
+  </si>
+  <si>
+    <t>（〜の）においがする</t>
+  </si>
+  <si>
+    <t>先生、博士</t>
+  </si>
+  <si>
+    <t>国際的な</t>
+  </si>
+  <si>
+    <t>午前</t>
+  </si>
+  <si>
+    <t>〜に反対して</t>
+  </si>
+  <si>
+    <t>〜を減らす</t>
+  </si>
+  <si>
+    <t>競技場</t>
+  </si>
+  <si>
+    <t>〜を発見する</t>
+  </si>
+  <si>
+    <t>〜に乗り遅れる、〜を逃す</t>
+  </si>
+  <si>
+    <t>大きさ</t>
+  </si>
+  <si>
+    <t>効果、結果</t>
+  </si>
+  <si>
+    <t>（雌）牛</t>
+  </si>
+  <si>
+    <t>4月</t>
+  </si>
+  <si>
+    <t>〜を定める、置く</t>
+  </si>
+  <si>
+    <t>舞台、ステージ</t>
+  </si>
+  <si>
+    <t>サービス</t>
+  </si>
+  <si>
+    <t>（人工）衛星</t>
+  </si>
+  <si>
+    <t>〜を傷つける、痛む</t>
+  </si>
+  <si>
+    <t>眺め、考え(方)</t>
+  </si>
+  <si>
+    <t>〜に触れる、接触</t>
+  </si>
+  <si>
+    <t>〜を紹介する</t>
+  </si>
+  <si>
+    <t>(ベルなど)を鳴らす、輪</t>
+  </si>
+  <si>
+    <t>警察</t>
+  </si>
+  <si>
+    <t>国家の、国民の</t>
+  </si>
+  <si>
+    <t>塩</t>
+  </si>
+  <si>
+    <t>〜を招く、招待する</t>
+  </si>
+  <si>
+    <t>プラスチック製の</t>
+  </si>
+  <si>
+    <t>運のよい、幸運な</t>
+  </si>
+  <si>
+    <t>乾いた、〜を乾かす</t>
+  </si>
+  <si>
+    <t>(ぴょんと)とぶ</t>
+  </si>
+  <si>
+    <t>細胞</t>
+  </si>
+  <si>
+    <t>3月</t>
+  </si>
+  <si>
+    <t>スキーをする、スキー板</t>
+  </si>
+  <si>
+    <t>文</t>
+  </si>
+  <si>
+    <t>〜を印刷する、印刷</t>
+  </si>
+  <si>
+    <t>大洋</t>
+  </si>
+  <si>
+    <t>ドル</t>
+  </si>
+  <si>
+    <t>増える、〜を増やす</t>
+  </si>
+  <si>
+    <t>運動、練習</t>
+  </si>
+  <si>
+    <t>主将、船長</t>
+  </si>
+  <si>
+    <t>バレーボール</t>
+  </si>
+  <si>
+    <t>肉</t>
+  </si>
+  <si>
+    <t>価格</t>
+  </si>
+  <si>
+    <t>距離</t>
+  </si>
+  <si>
+    <t>橋</t>
+  </si>
+  <si>
+    <t>イングランド</t>
+  </si>
+  <si>
+    <t>〜を導く、案内する</t>
+  </si>
+  <si>
+    <t>瞬間、ちょっとの間</t>
+  </si>
+  <si>
+    <t>髪の毛、毛</t>
+  </si>
+  <si>
+    <t>バナナ</t>
+  </si>
+  <si>
+    <t>深い</t>
+  </si>
+  <si>
+    <t>王、国王</t>
+  </si>
+  <si>
+    <t>戦争</t>
+  </si>
+  <si>
+    <t>食事</t>
+  </si>
+  <si>
+    <t>夫</t>
+  </si>
+  <si>
+    <t>6月</t>
+  </si>
+  <si>
+    <t>味、〜の味がする</t>
+  </si>
+  <si>
+    <t>太陽の</t>
+  </si>
+  <si>
+    <t>（〜を）洗う</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>水曜日</t>
+  </si>
+  <si>
+    <t>くつろぐ</t>
+  </si>
+  <si>
+    <t>〜を案内する、ガイド</t>
+  </si>
+  <si>
+    <t>キャンプする、キャンプ</t>
+  </si>
+  <si>
+    <t>火、火事</t>
+  </si>
+  <si>
+    <t>まじめな、深刻な</t>
+  </si>
+  <si>
+    <t>インド</t>
+  </si>
+  <si>
+    <t>地域社会、共同体</t>
+  </si>
+  <si>
+    <t>15の、15</t>
+  </si>
+  <si>
+    <t>期間、時代</t>
+  </si>
+  <si>
+    <t>岩、岩石</t>
+  </si>
+  <si>
+    <t>フランス</t>
+  </si>
+  <si>
+    <t>血、血液</t>
+  </si>
+  <si>
+    <t>クリスマス</t>
+  </si>
+  <si>
+    <t>キロメートル</t>
+  </si>
+  <si>
+    <t>〜を許す</t>
+  </si>
+  <si>
+    <t>初め、始まり</t>
+  </si>
+  <si>
+    <t>新鮮な</t>
+  </si>
+  <si>
+    <t>マラソン</t>
+  </si>
+  <si>
+    <t>火曜日</t>
+  </si>
+  <si>
+    <t>象徴</t>
+  </si>
+  <si>
+    <t>リンゴ</t>
+  </si>
+  <si>
+    <t>地球上の、国際的な</t>
+  </si>
+  <si>
+    <t>釣り</t>
+  </si>
+  <si>
+    <t>10月</t>
+  </si>
+  <si>
+    <t>黄色の、黄色</t>
+  </si>
+  <si>
+    <t>調査員、研究者</t>
+  </si>
+  <si>
+    <t>主な、主要な</t>
+  </si>
+  <si>
+    <t>公の、公共の</t>
+  </si>
+  <si>
+    <t>記事</t>
+  </si>
+  <si>
+    <t>（〜を）引く、引っ張る</t>
+  </si>
+  <si>
+    <t>形</t>
+  </si>
+  <si>
+    <t>まっすぐに、まっすぐな</t>
+  </si>
+  <si>
+    <t>（大型の）船</t>
+  </si>
+  <si>
+    <t>50の、50</t>
+  </si>
+  <si>
+    <t>9月</t>
+  </si>
+  <si>
+    <t>損害、被害、〜に損害を与える</t>
+  </si>
+  <si>
+    <t>惑星</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>relax</t>
+  </si>
+  <si>
+    <t>guide</t>
+  </si>
+  <si>
+    <t>camp</t>
+  </si>
+  <si>
+    <t>rock</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>fifty</t>
+  </si>
+  <si>
+    <t>wash</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>view</t>
+  </si>
+  <si>
+    <t>touch</t>
+  </si>
+  <si>
+    <t>introduce</t>
+  </si>
+  <si>
+    <t>ring</t>
+  </si>
+  <si>
+    <t>police</t>
+  </si>
+  <si>
+    <t>national</t>
+  </si>
+  <si>
+    <t>salt</t>
+  </si>
+  <si>
+    <t>invite</t>
+  </si>
+  <si>
+    <t>plastic</t>
+  </si>
+  <si>
+    <t>lucky</t>
+  </si>
+  <si>
+    <t>dry</t>
+  </si>
+  <si>
+    <t>jump</t>
+  </si>
+  <si>
+    <t>cell</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>ski</t>
+  </si>
+  <si>
     <t>sentence</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>word</t>
-  </si>
-  <si>
-    <t>meaning</t>
-  </si>
-  <si>
-    <t>（　　） your hands before you eat.</t>
-  </si>
-  <si>
-    <t>I will send you a （　　） of my family.</t>
-  </si>
-  <si>
-    <t>My father leaves the office at five on （　　）.</t>
-  </si>
-  <si>
-    <t>They (      　) after they had lunch in the park.</t>
-  </si>
-  <si>
-    <t>Lisa （　　） us around the school.</t>
-  </si>
-  <si>
-    <t>Our club goes （　　） every summer.</t>
-  </si>
-  <si>
-    <t>Don't get too close to the （　　）!</t>
-  </si>
-  <si>
-    <t>Keiko is （　　） about studying.</t>
-  </si>
-  <si>
-    <t>（　　） has a large population.</t>
-  </si>
-  <si>
-    <t>This event is open to everyone in the （　　）.</t>
-  </si>
-  <si>
-    <t>The school gate will close in （　　） minutes.</t>
-  </si>
-  <si>
-    <t>My aunt stayed with me for a short （　　）.</t>
-  </si>
-  <si>
-    <t>There are many （　　） on the mountain road.</t>
-  </si>
-  <si>
-    <t>（　　　） has many wonderful places to visit.</t>
-  </si>
-  <si>
-    <t>My （　　） type is A.</t>
-  </si>
-  <si>
-    <t>We will have a （　　） party next week.</t>
-  </si>
-  <si>
-    <t>The station is one （　　） away from here.</t>
-  </si>
-  <si>
-    <t>Smoking is not （　　） in this restaurant.</t>
-  </si>
-  <si>
-    <t>Mike will come to Japan at the （　　） of May.</t>
-  </si>
-  <si>
-    <t>These vegetables are very （　　）.</t>
-  </si>
-  <si>
-    <t>Takashi finished running the （　　）.</t>
-  </si>
-  <si>
-    <t>I have a piano lesson every （　　）.</t>
-  </si>
-  <si>
-    <t>This tower is a （　　） of our city.</t>
-  </si>
-  <si>
-    <t>An （　　） fell from the tree to the ground.</t>
-  </si>
-  <si>
-    <t>Our company has become （　　） recently.</t>
-  </si>
-  <si>
-    <t>I often go to the lake for （　　）.　</t>
-  </si>
-  <si>
-    <t>We have a Halloween party every （　　）.　　</t>
-  </si>
-  <si>
-    <t>We must stop when the traffic lights are （　　）.</t>
-  </si>
-  <si>
-    <t>The （　　） studies wild plants on the island　.</t>
-  </si>
-  <si>
-    <t>Her （　　） job is taking care of young children.</t>
-  </si>
-  <si>
-    <t>Have you ever used a （　　） telephone?</t>
-  </si>
-  <si>
-    <t>I read an interesting （　　） in the magazine.</t>
-  </si>
-  <si>
-    <t>Please （　　） the rope hard.</t>
-  </si>
-  <si>
-    <t>What （　　） is that building going to be?</t>
-  </si>
-  <si>
-    <t>Go （　　） down this street.</t>
-  </si>
-  <si>
-    <t>Those bananas came to Japan by （　　）.</t>
-  </si>
-  <si>
-    <t>（　　） cents is half of a dollar.</t>
-  </si>
-  <si>
-    <t>We go back to school in （　　）.</t>
-  </si>
-  <si>
-    <t>The typhoon caused great （　　） to the town.</t>
-  </si>
-  <si>
-    <t>The earth is the third （　　） from the sun.</t>
-  </si>
-  <si>
-    <t>Wash</t>
-  </si>
-  <si>
-    <t>photo</t>
-  </si>
-  <si>
-    <t>Wednesdays</t>
-  </si>
-  <si>
-    <t>relaxed</t>
-  </si>
-  <si>
-    <t>guided</t>
-  </si>
-  <si>
-    <t>camping</t>
-  </si>
-  <si>
-    <t>fire</t>
-  </si>
-  <si>
-    <t>serious</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>community</t>
-  </si>
-  <si>
-    <t>fifteen</t>
-  </si>
-  <si>
-    <t>period</t>
-  </si>
-  <si>
-    <t>rocks</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>blood</t>
-  </si>
-  <si>
-    <t>Christmas</t>
-  </si>
-  <si>
-    <t>kilometer</t>
-  </si>
-  <si>
-    <t>allowed</t>
-  </si>
-  <si>
-    <t>beginning</t>
-  </si>
-  <si>
-    <t>fresh</t>
-  </si>
-  <si>
-    <t>marathon</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>symbol</t>
-  </si>
-  <si>
-    <t>apple</t>
-  </si>
-  <si>
-    <t>global</t>
-  </si>
-  <si>
-    <t>fishing</t>
-  </si>
-  <si>
-    <t>October</t>
-  </si>
-  <si>
-    <t>yellow</t>
-  </si>
-  <si>
-    <t>researcher</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>public</t>
-  </si>
-  <si>
-    <t>article</t>
-  </si>
-  <si>
-    <t>pull</t>
-  </si>
-  <si>
-    <t>shape</t>
-  </si>
-  <si>
-    <t>straight</t>
-  </si>
-  <si>
-    <t>ship</t>
-  </si>
-  <si>
-    <t>Fifty</t>
-  </si>
-  <si>
-    <t>September</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>planet</t>
-  </si>
-  <si>
-    <t>食べる前に手を洗いなさい</t>
-  </si>
-  <si>
-    <t>私はあなたに私の家族の写真を1枚送ります</t>
-  </si>
-  <si>
-    <t>父は水曜日には5時に退社する</t>
-  </si>
-  <si>
-    <t>公園で昼食を食べたあと、彼らはくつろいだ</t>
-  </si>
-  <si>
-    <t>リサは学校じゅう私たちを案内してくれた</t>
-  </si>
-  <si>
-    <t>私たちのクラブは毎年夏にキャンプに行く</t>
-  </si>
-  <si>
-    <t>火に近づきすぎないで！</t>
-  </si>
-  <si>
-    <t>ケイコは学習に対してまじめである</t>
-  </si>
-  <si>
-    <t>インドは人口が多い</t>
-  </si>
-  <si>
-    <t>この行事は地域社会のすべての人に開放されている</t>
-  </si>
-  <si>
-    <t>校門はあと15分で閉まる</t>
-  </si>
-  <si>
-    <t>おばは短期間、私の家に滞在した</t>
-  </si>
-  <si>
-    <t>多くの岩が山道にある</t>
-  </si>
-  <si>
-    <t>フランスには多くの訪れるべき素晴らしい場所がある</t>
-  </si>
-  <si>
-    <t>私の血液型はA型だ</t>
-  </si>
-  <si>
-    <t>私たちは来週クリスマスパーティーを開く</t>
-  </si>
-  <si>
-    <t>駅はここから1キロメートル先だ</t>
-  </si>
-  <si>
-    <t>このレストランでは喫煙は許されていない</t>
-  </si>
-  <si>
-    <t>マイクは5月の初めに日本に来るだろう</t>
-  </si>
-  <si>
-    <t>これらの野菜はとても新鮮だ</t>
-  </si>
-  <si>
-    <t>タカシはマラソンを走り終えた</t>
-  </si>
-  <si>
-    <t>私は毎週火曜日にピアノのレッスンがある</t>
-  </si>
-  <si>
-    <t>この塔は私たちの市の象徴だ</t>
-  </si>
-  <si>
-    <t>リンゴが木から地面に落ちた</t>
-  </si>
-  <si>
-    <t>最近、私たちの会社は国際的になった</t>
-  </si>
-  <si>
-    <t>私はよく釣りをしに湖に行く</t>
-  </si>
-  <si>
-    <t>私たちは毎年10月にハロウィーンパーティーを開く</t>
-  </si>
-  <si>
-    <t>信号が黄色のときは、止まらなければならない</t>
-  </si>
-  <si>
-    <t>その研究者はその島の野生植物を研究している</t>
-  </si>
-  <si>
-    <t>彼女の主な仕事は幼い子どもたちの世話をすることだ</t>
-  </si>
-  <si>
-    <t>あなたは公衆電話を使ったことがありますか</t>
-  </si>
-  <si>
-    <t>私はその雑誌でおもしろい記事を読んだ</t>
-  </si>
-  <si>
-    <t>そのロープを強く引いてください</t>
-  </si>
-  <si>
-    <t>あの建物はどんな形になるのですか</t>
-  </si>
-  <si>
-    <t>この通りをまっすぐに行きなさい</t>
-  </si>
-  <si>
-    <t>それらのバナナは船で日本に来た</t>
-  </si>
-  <si>
-    <t>50セントは1ドルの半分だ</t>
-  </si>
-  <si>
-    <t>私たちは9月に学校に戻る</t>
-  </si>
-  <si>
-    <t>台風は町に大きな損害を及ぼした</t>
-  </si>
-  <si>
-    <t>地球は太陽から3番目の惑星だ</t>
+  </si>
+  <si>
+    <t>print</t>
+  </si>
+  <si>
+    <t>ocean</t>
+  </si>
+  <si>
+    <t>dollar</t>
+  </si>
+  <si>
+    <t>increase</t>
+  </si>
+  <si>
+    <t>exercise</t>
+  </si>
+  <si>
+    <t>captain</t>
+  </si>
+  <si>
+    <t>volleyball</t>
+  </si>
+  <si>
+    <t>meat</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>lead</t>
+  </si>
+  <si>
+    <t>moment</t>
+  </si>
+  <si>
+    <t>hair</t>
+  </si>
+  <si>
+    <t>banana</t>
+  </si>
+  <si>
+    <t>deep</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>war</t>
+  </si>
+  <si>
+    <t>meal</t>
+  </si>
+  <si>
+    <t>husband</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>taste</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>temple</t>
+  </si>
+  <si>
+    <t>exchange</t>
+  </si>
+  <si>
+    <t>smell</t>
+  </si>
+  <si>
+    <t>a.m. / A.M.</t>
+  </si>
+  <si>
+    <t>discover</t>
+  </si>
+  <si>
+    <t>miss</t>
+  </si>
+  <si>
+    <t>cow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,24 +1149,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -919,7 +1164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -971,29 +1216,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color auto="1"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color auto="1"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1003,7 +1237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,23 +1257,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1344,463 +1563,979 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="49.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="92.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
         <v>123</v>
       </c>
-      <c r="B1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A7" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A8" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A9" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A11" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A12" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A14" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A16" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A17" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A18" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A20" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A21" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A22" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A23" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A24" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A25" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A26" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A27" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A28" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A29" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A30" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A31" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A32" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A34" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A35" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A36" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A37" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A38" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A39" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A40" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A41" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A42" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A43" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A44" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A45" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A46" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A47" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A48" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A49" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A50" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A51" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A52" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A53" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A54" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A55" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A56" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A57" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A58" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A59" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A60" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A61" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A62" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A63" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A64" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A65" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A66" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A67" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A68" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A69" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A70" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A71" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A72" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A73" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A74" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A75" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A76" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A77" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A78" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A79" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A80" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A81" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A82" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A83" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B83" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A84" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A85" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A86" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A87" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A88" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B88" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A89" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B89" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A90" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B90" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A91" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B91" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A92" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B92" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A93" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B93" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A94" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A95" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B95" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A96" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B96" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A97" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B97" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A98" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B98" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A99" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A100" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B100" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A101" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B101" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A102" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B102" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A103" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B103" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A104" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B104" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A105" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B105" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A106" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A107" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B107" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A108" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B108" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A109" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B109" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A110" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B110" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A111" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B111" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A112" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B112" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A113" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="B113" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A114" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B114" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A115" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B115" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A116" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B116" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A117" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B117" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A118" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A119" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B119" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A120" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B120" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A121" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B121" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-english-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DFBEA1-29AE-4B10-ACA6-E30D147E2590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20F1BFA-DE7C-42B5-9E12-1EC175FB9450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="英単語リスト" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="368">
   <si>
     <t>例文</t>
   </si>
@@ -46,408 +46,100 @@
     <t>clear</t>
   </si>
   <si>
-    <t>私たちは彼からはっきりした答えを得る必要がある</t>
-  </si>
-  <si>
     <t>August</t>
   </si>
   <si>
-    <t>私の夏休みは8月10日からだ</t>
-  </si>
-  <si>
     <t>percent</t>
   </si>
   <si>
-    <t>これらの古本は今日は30パーセント引きだ</t>
-  </si>
-  <si>
-    <t>京都にいたとき、私は数多くの寺を訪れた</t>
-  </si>
-  <si>
     <t>cap</t>
   </si>
   <si>
-    <t>家の中に入るときは、帽子を脱ぎなさい</t>
-  </si>
-  <si>
     <t>past</t>
   </si>
   <si>
-    <t>私たちは過去に同じ問題を抱えていた</t>
-  </si>
-  <si>
     <t>temperature</t>
   </si>
   <si>
-    <t>この部屋の温度はあなたにとって快適ですか</t>
-  </si>
-  <si>
     <t>advice</t>
   </si>
   <si>
-    <t>おばは私に役に立つアドバイスをしてくれた</t>
-  </si>
-  <si>
     <t>nervous</t>
   </si>
   <si>
-    <t>私はとてもたくさんの人の前で緊張していた</t>
-  </si>
-  <si>
     <t>skill</t>
   </si>
   <si>
-    <t>彼は日本画のすばらしい技能を持っている</t>
-  </si>
-  <si>
     <t>common</t>
   </si>
   <si>
-    <t>英語は世界の共通語だ</t>
-  </si>
-  <si>
     <t>ceremony</t>
   </si>
   <si>
-    <t>学校の最初の日に式典があった</t>
-  </si>
-  <si>
     <t>delicious</t>
   </si>
   <si>
-    <t>今日、おいしい給食を食べた</t>
-  </si>
-  <si>
     <t>subject</t>
   </si>
   <si>
-    <t>あなたは何の科目が一番好きですか</t>
-  </si>
-  <si>
-    <t>私は彼と何度もEメールを交換した</t>
-  </si>
-  <si>
     <t>sugar</t>
   </si>
   <si>
-    <t>あなたはコーヒーに砂糖を入れますか</t>
-  </si>
-  <si>
     <t>adult</t>
   </si>
   <si>
-    <t>ケンはスーツを着ていると大人のように見える</t>
-  </si>
-  <si>
     <t>pen</t>
   </si>
   <si>
-    <t>黒のペンで名前を書いてください</t>
-  </si>
-  <si>
     <t>notebook</t>
   </si>
   <si>
-    <t>あなたのノートを見せてもらえますか</t>
-  </si>
-  <si>
     <t>wonder</t>
   </si>
   <si>
-    <t>アンはなぜパーティーに来なかったのだろうか</t>
-  </si>
-  <si>
     <t>communicate</t>
   </si>
   <si>
-    <t>多くの人々がEメールでコミュニケーションをとっている</t>
-  </si>
-  <si>
     <t>foot</t>
   </si>
   <si>
-    <t>彼女はテニスの試合で右足を痛めた</t>
-  </si>
-  <si>
-    <t>そのなべのスープはいいにおいがする</t>
-  </si>
-  <si>
     <t>Dr.</t>
   </si>
   <si>
-    <t>マツモト先生に診察していただきたいのですが</t>
-  </si>
-  <si>
     <t>international</t>
   </si>
   <si>
-    <t>私は国際的な祭りに行った</t>
-  </si>
-  <si>
-    <t>その店は午前10時30分に開店する</t>
-  </si>
-  <si>
     <t>against</t>
   </si>
   <si>
-    <t>父は留学するという私の計画に反対している</t>
-  </si>
-  <si>
     <t>reduce</t>
   </si>
   <si>
-    <t>私たちは製品のコストを減らさなければならない</t>
-  </si>
-  <si>
     <t>stadium</t>
   </si>
   <si>
-    <t>競技場はサッカーファンで混雑していた</t>
-  </si>
-  <si>
-    <t>彼は100年前に新しい惑星を発見した</t>
-  </si>
-  <si>
-    <t>昨夜、私は最終バスに乗り遅れて、タクシーに乗った</t>
-  </si>
-  <si>
     <t>size</t>
   </si>
   <si>
-    <t>このシャツのもっと小さいサイズはありますか</t>
-  </si>
-  <si>
     <t>effect</t>
   </si>
   <si>
-    <t>その薬は私に悪い効果をもたらした</t>
-  </si>
-  <si>
-    <t>農場で牛が草を食べている</t>
-  </si>
-  <si>
     <t>April</t>
   </si>
   <si>
-    <t>日本では学校は4月に始まる</t>
-  </si>
-  <si>
     <t>set</t>
   </si>
   <si>
-    <t>次回の練習試合の日程を決めましょう</t>
-  </si>
-  <si>
     <t>stage</t>
   </si>
   <si>
-    <t>私の大好きなバンドが舞台で演奏している</t>
-  </si>
-  <si>
     <t>service</t>
   </si>
   <si>
-    <t>そのホテルのサービスはすばらしかった</t>
-  </si>
-  <si>
     <t>satellite</t>
   </si>
   <si>
-    <t>月は地球の衛星だ</t>
-  </si>
-  <si>
     <t>hurt</t>
-  </si>
-  <si>
-    <t>彼はバスケットボールをしているときに腕を痛めた</t>
-  </si>
-  <si>
-    <t>We need to get a (         ) answer from him.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>My summer vacation is from  (         )  10th.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>These old books are 30  (         )  cheaper today.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>While I was in Kyoto, I visited many  (         ) .</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Take off your  (         )  when you enter the house.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>We had the same trouble in the  (         )  .</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Is the   (         )   in this room good for you?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>My aunt gave me some useful   (         )  .</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>I was   (         )   in front of so many people.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>He has great   (         )   in Japanese painting.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>English is the world's   (         )   language.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>There was a   (         )   on the first day of school.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>We had a   (         )   school lunch today.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>What   (         )   do you like the best?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>I   (         )   e-mails with him many times.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Do you put   (         )   in your coffee?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Ken looks like an   (         )   when he wears a suit.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Please write your name with a black   (         )  .</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Can you show me your   (         )  ?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>I   (         )   why Ann didn't come to the party.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Many people   (         )   by e-mail.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>She injured her right   (         )   in the tennis match.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>The soup in the pot   (         )   good.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>I'd like to see   (         )   Matsumoto.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>I went to an   (         )   festival.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">The store opens at 10:30   (         )  </t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>My father is   (         )   my plan to study abroad.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>We must   (         )   the cost of our product.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>The   (         )   was crowded with soccer fans.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>He   (         )   a new planet a hundred years ago.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Last night, I   (         )   the last bus and took a taxi.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Do you have this shirt in a smaller   (         )  ?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>The medicine had a bad   (         )   on me.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>The   (         )   are eating grass on the farm.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>School starts in   (         )   in Japan.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Let's   (         )   the date for the next practice game.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>My favorite band is playing on the   (         )  .</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>The   (         )   at the hotel was excellent.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>The moon is a   (         )   of the earth.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>He   (         )   his arm while he was playing basketball.</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>temples</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>exchanged</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>smells</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">a.m. </t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>discovered</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>missed</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>cows</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>空欄に入る答え</t>
@@ -1089,6 +781,375 @@
   </si>
   <si>
     <t>cow</t>
+  </si>
+  <si>
+    <t>One _____ on the train were a pink hat.</t>
+  </si>
+  <si>
+    <t>John and I have a close _____.</t>
+  </si>
+  <si>
+    <t>He drove across the _____.</t>
+  </si>
+  <si>
+    <t>My dog has caught a _____.</t>
+  </si>
+  <si>
+    <t>A _____ was standing close to the man.</t>
+  </si>
+  <si>
+    <t>He _____ an important report.</t>
+  </si>
+  <si>
+    <t>The little girl goes to sleep with a _____.</t>
+  </si>
+  <si>
+    <t>Our baseball team won the _____ last year.</t>
+  </si>
+  <si>
+    <t>_____ up, or you'll be late for school.</t>
+  </si>
+  <si>
+    <t>Aya looked at _____ in the mirror.</t>
+  </si>
+  <si>
+    <t>My grandfather was injured in a traffic _____.</t>
+  </si>
+  <si>
+    <t>Picasso was a great Spanish _____.</t>
+  </si>
+  <si>
+    <t>Let's make a _____ on a star.</t>
+  </si>
+  <si>
+    <t>We played volleyball in the _____ this afternoon.</t>
+  </si>
+  <si>
+    <t>Could you tell me your _____ for today?</t>
+  </si>
+  <si>
+    <t>The _____ told Tom to practice more.</t>
+  </si>
+  <si>
+    <t>He turned off the _____ before he left home.</t>
+  </si>
+  <si>
+    <t>This computer can store a lot of _____.</t>
+  </si>
+  <si>
+    <t>Our school is in the _____ of our town.</t>
+  </si>
+  <si>
+    <t>Our class won first prize in the _____ contest.</t>
+  </si>
+  <si>
+    <t>What is the _____ of your favorite book?</t>
+  </si>
+  <si>
+    <t>I want the _____ in the pet shop.</t>
+  </si>
+  <si>
+    <t>There was a _____ accident at the station.</t>
+  </si>
+  <si>
+    <t>Some people have a _____ of spiders.</t>
+  </si>
+  <si>
+    <t>_____ your hand and tell me the answer.</t>
+  </si>
+  <si>
+    <t>He kept the _____ of the meeting.</t>
+  </si>
+  <si>
+    <t>What time did you _____ up this morning?</t>
+  </si>
+  <si>
+    <t>We can tell the time from the _____ of the sun.</t>
+  </si>
+  <si>
+    <t>She explained her opinion very _____.</t>
+  </si>
+  <si>
+    <t>I have been to Rome _____.</t>
+  </si>
+  <si>
+    <t>_____ 24th is called Christmas Eve.</t>
+  </si>
+  <si>
+    <t>This is the _____ of our guests tonight.</t>
+  </si>
+  <si>
+    <t>Air _____ is a big problem in our city.</t>
+  </si>
+  <si>
+    <t>This temple is a World Heritage _____.</t>
+  </si>
+  <si>
+    <t>My father left home at the _____ time.</t>
+  </si>
+  <si>
+    <t>I believe this bag is _____.</t>
+  </si>
+  <si>
+    <t>Can I use your _____ this afternoon?</t>
+  </si>
+  <si>
+    <t>She passed the exam with the _____ effort.</t>
+  </si>
+  <si>
+    <t>My grandfather has been _____ for five years.</t>
+  </si>
+  <si>
+    <t>He usually takes a _____ at eleven o'clock.</t>
+  </si>
+  <si>
+    <t>My son was very _____ when he was little.</t>
+  </si>
+  <si>
+    <t>列車の中のひとりの婦人がピンクの帽子をかぶっていた。</t>
+  </si>
+  <si>
+    <t>ジョンと私の間には強い友情がある。</t>
+  </si>
+  <si>
+    <t>彼は砂漠を車で横断した。</t>
+  </si>
+  <si>
+    <t>私のイヌは病気にかかった。</t>
+  </si>
+  <si>
+    <t>クマが男の人の近くに立っていた。</t>
+  </si>
+  <si>
+    <t>彼は重要な報告書を完成した。</t>
+  </si>
+  <si>
+    <t>その幼い少女は人形と一緒に眠る。</t>
+  </si>
+  <si>
+    <t>私たちの野球チームは昨年、トーナメントで優勝した。</t>
+  </si>
+  <si>
+    <t>急いで、でないと学校に遅れますよ。</t>
+  </si>
+  <si>
+    <t>アヤは鏡で自分を見た。</t>
+  </si>
+  <si>
+    <t>祖父は交通事故でけがをした。</t>
+  </si>
+  <si>
+    <t>ピカソはスペインの偉大な芸術家だった。</t>
+  </si>
+  <si>
+    <t>星に願いをかけましょう。</t>
+  </si>
+  <si>
+    <t>私たちは今日の午後、体育館でバレーボールをした。</t>
+  </si>
+  <si>
+    <t>今日のあなたの予定を教えていただけますか。</t>
+  </si>
+  <si>
+    <t>監督はトムにもっと練習するように言った。</t>
+  </si>
+  <si>
+    <t>彼は家を出る前にガスを止めた。</t>
+  </si>
+  <si>
+    <t>このコンピュータはたくさんのデータを保存することができる。</t>
+  </si>
+  <si>
+    <t>私たちの学校は町の北部にある。</t>
+  </si>
+  <si>
+    <t>私たちのクラスは合唱コンテストで優勝した。</t>
+  </si>
+  <si>
+    <t>あなたの大好きな本の題名は何ですか。</t>
+  </si>
+  <si>
+    <t>私はペットショップの子イヌがほしい。</t>
+  </si>
+  <si>
+    <t>駅で恐ろしい事故があった。</t>
+  </si>
+  <si>
+    <t>クモを恐れる人もいる。</t>
+  </si>
+  <si>
+    <t>手を挙げて答えを言ってください。</t>
+  </si>
+  <si>
+    <t>彼はその会議の記録をとった。</t>
+  </si>
+  <si>
+    <t>今朝は何時に目がさめですか。</t>
+  </si>
+  <si>
+    <t>太陽の位置から時間がわかる。</t>
+  </si>
+  <si>
+    <t>彼女は自分の意見をとてもはっきりと説明した。</t>
+  </si>
+  <si>
+    <t>私はローマに2度行ったことがある。</t>
+  </si>
+  <si>
+    <t>12月24日はクリスマス・イブと呼ばれる。</t>
+  </si>
+  <si>
+    <t>これは今夜の招待客のリストだ。</t>
+  </si>
+  <si>
+    <t>大気汚染は私たちの市の大きな問題だ。</t>
+  </si>
+  <si>
+    <t>この寺は世界遺産だ。</t>
+  </si>
+  <si>
+    <t>父はいつもの時間に家を出た。</t>
+  </si>
+  <si>
+    <t>このかばんはきっとあなたのだと思う。</t>
+  </si>
+  <si>
+    <t>今日の午後、あなたのカメラを使ってもいいですか。</t>
+  </si>
+  <si>
+    <t>彼女は最小限の努力で試験に合格した。</t>
+  </si>
+  <si>
+    <t>祖父が亡くなって5年になる。</t>
+  </si>
+  <si>
+    <t>彼はふつう11時にお風呂に入る。</t>
+  </si>
+  <si>
+    <t>息子は幼いころ、とても内気だった。</t>
+  </si>
+  <si>
+    <t>lady</t>
+  </si>
+  <si>
+    <t>friendship</t>
+  </si>
+  <si>
+    <t>desert</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>bear</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>doll</t>
+  </si>
+  <si>
+    <t>tournament</t>
+  </si>
+  <si>
+    <t>Hurry</t>
+  </si>
+  <si>
+    <t>herself</t>
+  </si>
+  <si>
+    <t>accident</t>
+  </si>
+  <si>
+    <t>artist</t>
+  </si>
+  <si>
+    <t>wish</t>
+  </si>
+  <si>
+    <t>gym</t>
+  </si>
+  <si>
+    <t>schedule</t>
+  </si>
+  <si>
+    <t>coach</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>north</t>
+  </si>
+  <si>
+    <t>chorus</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>puppy</t>
+  </si>
+  <si>
+    <t>terrible</t>
+  </si>
+  <si>
+    <t>fear</t>
+  </si>
+  <si>
+    <t>Raise</t>
+  </si>
+  <si>
+    <t>records</t>
+  </si>
+  <si>
+    <t>wake</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>clearly</t>
+  </si>
+  <si>
+    <t>twice</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>pollution</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>usual</t>
+  </si>
+  <si>
+    <t>yours</t>
+  </si>
+  <si>
+    <t>camera</t>
+  </si>
+  <si>
+    <t>least</t>
+  </si>
+  <si>
+    <t>dead</t>
+  </si>
+  <si>
+    <t>bath</t>
+  </si>
+  <si>
+    <t>shy</t>
   </si>
 </sst>
 </file>
@@ -1572,15 +1633,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="9" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>2</v>
@@ -1588,954 +1649,954 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="9" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="9" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>325</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="9" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="9" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="9" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="9" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="9" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="9" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="9" t="s">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="9" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="9" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="9" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>326</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="9" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="9" t="s">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="9" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="9" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="9" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>327</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="9" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="9" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="9" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="9" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="9" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>329</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="9" t="s">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>330</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="9" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="9" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="9" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" s="9" t="s">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="9" t="s">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="9" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>285</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="9" t="s">
-        <v>198</v>
+        <v>111</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>286</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="9" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>287</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="9" t="s">
-        <v>200</v>
+        <v>113</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>288</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="9" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>289</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="9" t="s">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>290</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="9" t="s">
-        <v>203</v>
+        <v>116</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>291</v>
+        <v>204</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" s="9" t="s">
-        <v>204</v>
+        <v>117</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50" s="9" t="s">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>293</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51" s="9" t="s">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>294</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52" s="9" t="s">
-        <v>207</v>
+        <v>120</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>295</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53" s="9" t="s">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54" s="9" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>297</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55" s="9" t="s">
-        <v>210</v>
+        <v>123</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>298</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56" s="9" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>299</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57" s="9" t="s">
-        <v>212</v>
+        <v>125</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58" s="9" t="s">
-        <v>213</v>
+        <v>126</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>301</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59" s="9" t="s">
-        <v>214</v>
+        <v>127</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>302</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60" s="9" t="s">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>303</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61" s="9" t="s">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>304</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62" s="9" t="s">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>305</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63" s="9" t="s">
-        <v>218</v>
+        <v>131</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>306</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64" s="9" t="s">
-        <v>219</v>
+        <v>132</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>307</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A65" s="9" t="s">
-        <v>220</v>
+        <v>133</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>308</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A66" s="9" t="s">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>309</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A67" s="9" t="s">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>310</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A68" s="9" t="s">
-        <v>223</v>
+        <v>136</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>311</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A69" s="9" t="s">
-        <v>224</v>
+        <v>137</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>312</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A70" s="9" t="s">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A71" s="9" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>314</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A72" s="9" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>315</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A73" s="9" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>316</v>
+        <v>229</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A74" s="9" t="s">
-        <v>229</v>
+        <v>142</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>317</v>
+        <v>230</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A75" s="9" t="s">
-        <v>230</v>
+        <v>143</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>318</v>
+        <v>231</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A76" s="9" t="s">
-        <v>231</v>
+        <v>144</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>319</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A77" s="9" t="s">
-        <v>232</v>
+        <v>145</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>320</v>
+        <v>233</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A78" s="9" t="s">
-        <v>233</v>
+        <v>146</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A79" s="9" t="s">
-        <v>234</v>
+        <v>147</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>322</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A80" s="9" t="s">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>323</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A81" s="9" t="s">
-        <v>236</v>
+        <v>149</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A82" s="9" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>284</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A83" s="9" t="s">
-        <v>238</v>
+        <v>151</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A84" s="9" t="s">
-        <v>239</v>
+        <v>152</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>277</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A85" s="9" t="s">
-        <v>240</v>
+        <v>153</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>278</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A86" s="9" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>279</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A87" s="9" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>280</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A88" s="9" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A89" s="9" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A90" s="9" t="s">
-        <v>245</v>
+        <v>158</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A91" s="9" t="s">
-        <v>246</v>
+        <v>159</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A92" s="9" t="s">
-        <v>247</v>
+        <v>160</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A93" s="9" t="s">
-        <v>248</v>
+        <v>161</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A94" s="9" t="s">
-        <v>249</v>
+        <v>162</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>281</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A95" s="9" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A96" s="9" t="s">
-        <v>251</v>
+        <v>164</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A97" s="9" t="s">
-        <v>252</v>
+        <v>165</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A98" s="9" t="s">
-        <v>253</v>
+        <v>166</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A99" s="9" t="s">
-        <v>254</v>
+        <v>167</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>282</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A100" s="9" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A101" s="9" t="s">
-        <v>256</v>
+        <v>169</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A102" s="9" t="s">
-        <v>257</v>
+        <v>170</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A103" s="9" t="s">
-        <v>258</v>
+        <v>171</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A104" s="9" t="s">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A105" s="9" t="s">
-        <v>260</v>
+        <v>173</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A106" s="9" t="s">
-        <v>261</v>
+        <v>174</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A107" s="9" t="s">
-        <v>262</v>
+        <v>175</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>143</v>
+        <v>56</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A108" s="9" t="s">
-        <v>263</v>
+        <v>176</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A109" s="9" t="s">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A110" s="9" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A111" s="9" t="s">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A112" s="9" t="s">
-        <v>267</v>
+        <v>180</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>148</v>
+        <v>61</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A113" s="9" t="s">
-        <v>268</v>
+        <v>181</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A114" s="9" t="s">
-        <v>269</v>
+        <v>182</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A115" s="9" t="s">
-        <v>270</v>
+        <v>183</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A116" s="9" t="s">
-        <v>271</v>
+        <v>184</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A117" s="9" t="s">
-        <v>272</v>
+        <v>185</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A118" s="9" t="s">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>283</v>
+        <v>196</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A119" s="9" t="s">
-        <v>274</v>
+        <v>187</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A120" s="9" t="s">
-        <v>275</v>
+        <v>188</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A121" s="9" t="s">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2566,450 +2627,460 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>3</v>
+        <v>286</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>76</v>
+        <v>246</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>5</v>
+        <v>287</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>4</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>7</v>
+        <v>288</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>6</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>289</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>115</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>290</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>9</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>11</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>292</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>13</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>18</v>
+        <v>294</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>84</v>
+        <v>254</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>21</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>24</v>
+        <v>297</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>23</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>87</v>
+        <v>257</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>26</v>
+        <v>298</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>88</v>
+        <v>258</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>28</v>
+        <v>299</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>27</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>89</v>
+        <v>259</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>29</v>
+        <v>300</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>116</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>31</v>
+        <v>301</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>30</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
-        <v>91</v>
+        <v>261</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>32</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>35</v>
+        <v>303</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>34</v>
+        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>93</v>
+        <v>263</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>37</v>
+        <v>304</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
-        <v>94</v>
+        <v>264</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>39</v>
+        <v>305</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>38</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
-        <v>95</v>
+        <v>265</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>41</v>
+        <v>306</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>40</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
-        <v>96</v>
+        <v>266</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>44</v>
+        <v>308</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>117</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>45</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
-        <v>99</v>
+        <v>269</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>48</v>
+        <v>310</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>47</v>
+        <v>351</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>49</v>
+        <v>311</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>118</v>
+        <v>352</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7" t="s">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>51</v>
+        <v>312</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>50</v>
+        <v>353</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7" t="s">
-        <v>102</v>
+        <v>272</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>53</v>
+        <v>313</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>52</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7" t="s">
-        <v>103</v>
+        <v>273</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>55</v>
+        <v>314</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>54</v>
+        <v>355</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7" t="s">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>56</v>
+        <v>315</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>119</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>57</v>
+        <v>316</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>120</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>59</v>
+        <v>317</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>58</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>61</v>
+        <v>318</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>60</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
-        <v>108</v>
+        <v>278</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>62</v>
+        <v>319</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>121</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>64</v>
+        <v>320</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>63</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>66</v>
+        <v>321</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>65</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
-        <v>111</v>
+        <v>281</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>68</v>
+        <v>322</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>67</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>70</v>
+        <v>323</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="7" t="s">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>72</v>
+        <v>324</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>71</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>114</v>
+        <v>284</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>74</v>
+        <v>325</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masahiro inui\Desktop\my-english-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4221D6-01C3-4485-B9E2-99DA2BC0C376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE770776-4828-4D64-BB99-AF78E15A380C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>meaning</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Our class won first prize in the _____ contest.</t>
   </si>
   <si>
-    <t>What is the _____ of your favorite book?</t>
-  </si>
-  <si>
     <t>I want the _____ in the pet shop.</t>
   </si>
   <si>
@@ -222,9 +219,6 @@
     <t>私たちのクラスは合唱コンテストで優勝した。</t>
   </si>
   <si>
-    <t>あなたの大好きな本の題名は何ですか。</t>
-  </si>
-  <si>
     <t>私はペットショップの子イヌがほしい。</t>
   </si>
   <si>
@@ -343,9 +337,6 @@
   </si>
   <si>
     <t>chorus</t>
-  </si>
-  <si>
-    <t>title</t>
   </si>
   <si>
     <t>puppy</t>
@@ -866,20 +857,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="51.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="50" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="46.25" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -890,10 +881,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -902,10 +893,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7"/>
     </row>
@@ -914,10 +905,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="7"/>
     </row>
@@ -926,10 +917,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="7"/>
     </row>
@@ -938,10 +929,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="7"/>
     </row>
@@ -950,10 +941,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="7"/>
     </row>
@@ -962,10 +953,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="7"/>
     </row>
@@ -974,10 +965,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="7"/>
     </row>
@@ -986,10 +977,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -998,10 +989,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="7"/>
     </row>
@@ -1010,10 +1001,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="7"/>
     </row>
@@ -1022,10 +1013,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="7"/>
     </row>
@@ -1034,10 +1025,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="7"/>
     </row>
@@ -1046,10 +1037,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="7"/>
     </row>
@@ -1058,10 +1049,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="7"/>
     </row>
@@ -1070,10 +1061,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="7"/>
     </row>
@@ -1082,10 +1073,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="7"/>
     </row>
@@ -1094,10 +1085,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="7"/>
     </row>
@@ -1106,10 +1097,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="7"/>
     </row>
@@ -1118,10 +1109,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" s="7"/>
     </row>
@@ -1130,10 +1121,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="7"/>
     </row>
@@ -1142,10 +1133,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D23" s="7"/>
     </row>
@@ -1154,10 +1145,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" s="7"/>
     </row>
@@ -1166,10 +1157,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25" s="7"/>
     </row>
@@ -1178,10 +1169,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26" s="7"/>
     </row>
@@ -1190,10 +1181,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" s="7"/>
     </row>
@@ -1202,10 +1193,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="7"/>
     </row>
@@ -1214,10 +1205,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" s="7"/>
     </row>
@@ -1226,10 +1217,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D30" s="7"/>
     </row>
@@ -1238,10 +1229,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" s="7"/>
     </row>
@@ -1250,10 +1241,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" s="7"/>
     </row>
@@ -1262,10 +1253,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" s="7"/>
     </row>
@@ -1274,10 +1265,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34" s="7"/>
     </row>
@@ -1286,10 +1277,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="7"/>
     </row>
@@ -1298,10 +1289,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D36" s="7"/>
     </row>
@@ -1310,10 +1301,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="7"/>
     </row>
@@ -1322,10 +1313,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D38" s="7"/>
     </row>
@@ -1334,52 +1325,40 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39" s="7"/>
-    </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C40" s="7" t="s">
+      <c r="C41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="8"/>
-    </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" s="1"/>
-    </row>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.27559055118110237" header="0.31496062992125984" footer="0.31496062992125984"/>
